--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -794,12 +794,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>343630.2303984007</v>
+        <v>343630</v>
       </c>
       <c r="R3" t="n">
-        <v>6454547.985617772</v>
+        <v>6454548</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -864,19 +859,9 @@
           <t>1990-08-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1990-08-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +895,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>96369</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -947,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>343630.2303984007</v>
+        <v>343630</v>
       </c>
       <c r="R4" t="n">
-        <v>6454547.985617772</v>
+        <v>6454548</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -980,19 +960,9 @@
           <t>1990-08-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1990-08-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,12 +996,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97451</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>343630.2303984007</v>
+        <v>343630</v>
       </c>
       <c r="R5" t="n">
-        <v>6454547.985617772</v>
+        <v>6454548</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1096,19 +1061,9 @@
           <t>1990-08-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1990-08-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,12 +1097,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>103225</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105570</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,10 +1129,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>343630.2303984007</v>
+        <v>343630</v>
       </c>
       <c r="R6" t="n">
-        <v>6454547.985617772</v>
+        <v>6454548</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1212,19 +1162,9 @@
           <t>1990-08-05</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1990-08-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>103812</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>343630.2303984007</v>
+        <v>343630</v>
       </c>
       <c r="R2" t="n">
-        <v>6454547.985617772</v>
+        <v>6454548</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>1990-08-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-08-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1198,12 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>96353</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>343630.2303984007</v>
+        <v>343630</v>
       </c>
       <c r="R7" t="n">
-        <v>6454547.985617772</v>
+        <v>6454548</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1268,19 +1248,9 @@
           <t>1990-08-05</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1990-08-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106169</v>
+        <v>106181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>97448</v>
+        <v>97454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98608</v>
+        <v>98616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>97451</v>
+        <v>97457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105570</v>
+        <v>105582</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106181</v>
+        <v>106190</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98616</v>
+        <v>98622</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>97457</v>
+        <v>97463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105582</v>
+        <v>105591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98600</v>
+        <v>98606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106190</v>
+        <v>106202</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98622</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105591</v>
+        <v>105603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106202</v>
+        <v>106211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105603</v>
+        <v>105612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106211</v>
+        <v>106216</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98628</v>
+        <v>98629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105612</v>
+        <v>105615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106216</v>
+        <v>106244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98629</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105615</v>
+        <v>105643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98613</v>
+        <v>98640</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106244</v>
+        <v>106250</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>98662</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105643</v>
+        <v>105649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98640</v>
+        <v>98646</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106250</v>
+        <v>106257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98662</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105649</v>
+        <v>105656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98646</v>
+        <v>98653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106257</v>
+        <v>106261</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98673</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105656</v>
+        <v>105660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>3281666</v>
       </c>
       <c r="B2" t="n">
-        <v>106261</v>
+        <v>106268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>4199824</v>
       </c>
       <c r="B3" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
         <v>2940734</v>
       </c>
       <c r="B4" t="n">
-        <v>98673</v>
+        <v>98680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
         <v>4238351</v>
       </c>
       <c r="B5" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>116328</v>
       </c>
       <c r="B6" t="n">
-        <v>105660</v>
+        <v>105667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>4293121</v>
       </c>
       <c r="B7" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1180,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4293121</v>
+        <v>4160493</v>
       </c>
       <c r="B7" t="n">
-        <v>98667</v>
+        <v>97511</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,23 +1191,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>221944</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1281,53 +1277,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116329</v>
+        <v>4293121</v>
       </c>
       <c r="B8" t="n">
-        <v>103226</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>340</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ryl</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chimaphila umbellata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) W. P. C. Barton</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>KULLEN, 500 m V om , Vg</t>
+          <t>Skog, torprest 500 m V om KULLEN, Vg</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>343444.2211115145</v>
+        <v>343630</v>
       </c>
       <c r="R8" t="n">
-        <v>6454441.914431312</v>
+        <v>6454548</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1349,29 +1340,14 @@
           <t>Väne-Åsaka</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>OV-Tro-0585</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
           <t>1990-08-05</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1990-08-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,15 +1362,136 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Mora Aronsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lennart Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Västergötlands flora 2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>116329</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103226</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>340</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ryl</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chimaphila umbellata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) W. P. C. Barton</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>KULLEN, 500 m V om , Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>343444.2211115145</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6454441.914431312</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Trollhättan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Väne-Åsaka</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>OV-Tro-0585</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1990-08-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>1990-08-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Enar Sahlin</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Lennart Andersson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
         </is>

--- a/artfynd/A 68519-2021 artfynd.xlsx
+++ b/artfynd/A 68519-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116328</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116329</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2940734</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3281666</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4160493</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4199824</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1380,6 +1415,11 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4238351</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,8 +1521,23 @@
           <t>Västergötlands flora 2002</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4293121</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>